--- a/ЛР2-3_Объем_рынка/Excel/СВ_сверху_вниз_снизу_вверх_NotaCode.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/СВ_сверху_вниз_снизу_вверх_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A608E716-6C8C-4B17-BA1D-032B8F8874E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE52871D-9D1F-4763-A941-0F5EC49A72D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,20 @@
     <sheet name="08_Источники" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1257,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
@@ -1288,7 +1302,7 @@
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
     </row>
-    <row r="4" spans="1:8" ht="43.5">
+    <row r="4" spans="1:8" ht="40.9">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1296,7 +1310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="29.25">
+    <row r="5" spans="1:8" ht="27.4">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1304,7 +1318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="43.5">
+    <row r="6" spans="1:8" ht="40.9">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -1312,7 +1326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="29.25">
+    <row r="7" spans="1:8" ht="27.4">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -1320,7 +1334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="29.25">
+    <row r="8" spans="1:8" ht="27.4">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -1439,7 +1453,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1489,7 +1503,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="71.25">
+    <row r="5" spans="1:6" ht="67.5">
       <c r="A5" s="12" t="s">
         <v>38</v>
       </c>
@@ -1543,7 +1557,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28.5">
+    <row r="8" spans="1:6" ht="27">
       <c r="A8" s="12" t="s">
         <v>50</v>
       </c>
@@ -1563,7 +1577,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.5">
+    <row r="9" spans="1:6" ht="27">
       <c r="A9" s="12" t="s">
         <v>53</v>
       </c>
@@ -1583,7 +1597,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.5">
+    <row r="10" spans="1:6" ht="27">
       <c r="A10" s="12" t="s">
         <v>57</v>
       </c>
@@ -1603,7 +1617,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="42.75">
+    <row r="11" spans="1:6" ht="40.5">
       <c r="A11" s="12" t="s">
         <v>61</v>
       </c>
@@ -1643,7 +1657,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.5">
+    <row r="13" spans="1:6" ht="27">
       <c r="A13" s="12" t="s">
         <v>64</v>
       </c>
@@ -1735,7 +1749,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -1789,7 +1803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="57">
+    <row r="5" spans="1:7" ht="40.5">
       <c r="A5" s="12" t="s">
         <v>84</v>
       </c>
@@ -1812,7 +1826,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.5">
+    <row r="6" spans="1:7" ht="27">
       <c r="A6" s="12" t="s">
         <v>86</v>
       </c>
@@ -1858,7 +1872,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.5">
+    <row r="8" spans="1:7" ht="27">
       <c r="A8" s="12" t="s">
         <v>88</v>
       </c>
@@ -1881,7 +1895,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.5">
+    <row r="9" spans="1:7" ht="27">
       <c r="A9" s="12" t="s">
         <v>89</v>
       </c>
@@ -1994,7 +2008,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -2067,7 +2081,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="57">
+    <row r="5" spans="1:10" ht="40.5">
       <c r="A5" s="12" t="s">
         <v>245</v>
       </c>
@@ -2101,7 +2115,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="42.75">
+    <row r="6" spans="1:10" ht="40.5">
       <c r="A6" s="12" t="s">
         <v>247</v>
       </c>
@@ -2135,7 +2149,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="42.75">
+    <row r="7" spans="1:10" ht="40.5">
       <c r="A7" s="12" t="s">
         <v>249</v>
       </c>
@@ -2258,7 +2272,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -2346,7 +2360,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="71.25">
+    <row r="5" spans="1:13" ht="67.5">
       <c r="A5" s="27" t="s">
         <v>251</v>
       </c>
@@ -2384,13 +2398,13 @@
         <v>252</v>
       </c>
       <c r="L5" s="36">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="M5" s="28" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="57">
+    <row r="6" spans="1:13" ht="54">
       <c r="A6" s="27" t="s">
         <v>254</v>
       </c>
@@ -2428,13 +2442,13 @@
         <v>255</v>
       </c>
       <c r="L6" s="36">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="M6" s="28" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="71.25">
+    <row r="7" spans="1:13" ht="67.5">
       <c r="A7" s="27" t="s">
         <v>256</v>
       </c>
@@ -2472,13 +2486,13 @@
         <v>257</v>
       </c>
       <c r="L7" s="36">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="M7" s="28" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="85.5">
+    <row r="8" spans="1:13" ht="81">
       <c r="A8" s="27" t="s">
         <v>258</v>
       </c>
@@ -2516,7 +2530,7 @@
         <v>259</v>
       </c>
       <c r="L8" s="36">
-        <v>46294.916666666664</v>
+        <v>46294.875</v>
       </c>
       <c r="M8" s="28" t="s">
         <v>261</v>
@@ -2707,7 +2721,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -3023,7 +3037,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -3083,7 +3097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.5">
+    <row r="5" spans="1:8" ht="27">
       <c r="A5" s="12" t="s">
         <v>159</v>
       </c>
@@ -3112,7 +3126,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.5">
+    <row r="6" spans="1:8" ht="27">
       <c r="A6" s="12" t="s">
         <v>164</v>
       </c>
@@ -3251,7 +3265,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -3389,7 +3403,7 @@
         <v>13726.834286313844</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="28.5">
+    <row r="8" spans="1:8" ht="27">
       <c r="A8" s="12" t="s">
         <v>188</v>
       </c>
@@ -3401,7 +3415,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28.5">
+    <row r="9" spans="1:8" ht="27">
       <c r="A9" s="12" t="s">
         <v>190</v>
       </c>
@@ -3493,7 +3507,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -3555,7 +3569,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="57">
+    <row r="5" spans="1:8" ht="54">
       <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
@@ -3581,7 +3595,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.5">
+    <row r="6" spans="1:8" ht="27">
       <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
@@ -3607,7 +3621,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.5">
+    <row r="7" spans="1:8" ht="27">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
@@ -3633,7 +3647,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="28.5">
+    <row r="8" spans="1:8" ht="27">
       <c r="A8" s="12" t="s">
         <v>219</v>
       </c>
@@ -3655,7 +3669,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="28.5">
+    <row r="9" spans="1:8">
       <c r="A9" s="12" t="s">
         <v>224</v>
       </c>
